--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -288,13 +288,13 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="H6">
         <v>81</v>
       </c>
       <c r="I6">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -7094,7 +7094,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  37/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  42/81 full</t>
         </is>
       </c>
     </row>
@@ -7374,6 +7374,21 @@
           <t xml:space="preserve">LNCX p19</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+24</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+24</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7384,6 +7399,16 @@
       <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">kkk</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX p21</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX p21</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -9,16 +9,16 @@
     <sheet name="ONGOING" sheetId="5" r:id="rId5"/>
     <sheet name="UMUT CELLS -4-" sheetId="6" r:id="rId6"/>
     <sheet name="Common Box #1" sheetId="7" r:id="rId7"/>
-    <sheet name="-80 Box1" sheetId="8" r:id="rId8"/>
-    <sheet name="-80 Box2" sheetId="9" r:id="rId9"/>
-    <sheet name="-80 Box3" sheetId="10" r:id="rId10"/>
-    <sheet name="-80 Box4" sheetId="11" r:id="rId11"/>
-    <sheet name="-80 Box5" sheetId="12" r:id="rId12"/>
-    <sheet name="-80 Box6" sheetId="13" r:id="rId13"/>
-    <sheet name="LiqNitro 1" sheetId="14" r:id="rId14"/>
-    <sheet name="LiqNitro 2" sheetId="15" r:id="rId15"/>
-    <sheet name="Beyza Caa Hücre Box 1" sheetId="16" r:id="rId16"/>
-    <sheet name="Beyza Caa Sıvı Azot Box 1" sheetId="17" r:id="rId17"/>
+    <sheet name="LiqNitro 1" sheetId="8" r:id="rId8"/>
+    <sheet name="LiqNitro 2" sheetId="9" r:id="rId9"/>
+    <sheet name="Beyza Caa Hücre Box 1" sheetId="10" r:id="rId10"/>
+    <sheet name="Beyza Caa Sıvı Azot Box 1" sheetId="11" r:id="rId11"/>
+    <sheet name="-80 Box1" sheetId="12" r:id="rId12"/>
+    <sheet name="-80 Box2" sheetId="13" r:id="rId13"/>
+    <sheet name="-80 Box3" sheetId="14" r:id="rId14"/>
+    <sheet name="-80 Box4" sheetId="15" r:id="rId15"/>
+    <sheet name="-80 Box5" sheetId="16" r:id="rId16"/>
+    <sheet name="-80 Box6" sheetId="17" r:id="rId17"/>
     <sheet name="Beyza Caa Hücre Box 2" sheetId="18" r:id="rId18"/>
   </sheets>
 </workbook>
@@ -251,13 +251,13 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5">
         <v>81</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -288,13 +288,13 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H6">
         <v>81</v>
       </c>
       <c r="I6">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -305,7 +305,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen → Rack 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1</t>
+          <t xml:space="preserve">LiqNitro 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -362,29 +362,29 @@
         <v>9</v>
       </c>
       <c r="G8">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="H8">
         <v>81</v>
       </c>
       <c r="I8">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen → Rack 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2</t>
+          <t xml:space="preserve">LiqNitro 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -399,34 +399,34 @@
         <v>9</v>
       </c>
       <c r="G9">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H9">
         <v>81</v>
       </c>
       <c r="I9">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen → Rack 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">baris</t>
+          <t xml:space="preserve">beyzat</t>
         </is>
       </c>
       <c r="E10">
@@ -436,34 +436,34 @@
         <v>9</v>
       </c>
       <c r="G10">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H10">
         <v>81</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen → Rack 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">baris</t>
+          <t xml:space="preserve">beyzat</t>
         </is>
       </c>
       <c r="E11">
@@ -473,29 +473,29 @@
         <v>9</v>
       </c>
       <c r="G11">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="H11">
         <v>81</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5</t>
+          <t xml:space="preserve">-80 Box1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -510,29 +510,29 @@
         <v>9</v>
       </c>
       <c r="G12">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="H12">
         <v>81</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6</t>
+          <t xml:space="preserve">-80 Box2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -547,29 +547,29 @@
         <v>9</v>
       </c>
       <c r="G13">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="H13">
         <v>81</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1</t>
+          <t xml:space="preserve">-80 Box3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -584,29 +584,29 @@
         <v>9</v>
       </c>
       <c r="G14">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="H14">
         <v>81</v>
       </c>
       <c r="I14">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2</t>
+          <t xml:space="preserve">-80 Box4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -621,34 +621,34 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H15">
         <v>81</v>
       </c>
       <c r="I15">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+          <t xml:space="preserve">-80 Box5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">beyzat</t>
+          <t xml:space="preserve">baris</t>
         </is>
       </c>
       <c r="E16">
@@ -658,34 +658,34 @@
         <v>9</v>
       </c>
       <c r="G16">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="H16">
         <v>81</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+          <t xml:space="preserve">-80 Box6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">beyzat</t>
+          <t xml:space="preserve">baris</t>
         </is>
       </c>
       <c r="E17">
@@ -695,24 +695,24 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="H17">
         <v>81</v>
       </c>
       <c r="I17">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Beyza Shelf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -751,14 +751,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen → Rack 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box3  ·  baris  ·  79/81 full</t>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1  ·  beyzat  ·  81/81 full</t>
         </is>
       </c>
     </row>
@@ -818,47 +818,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR fluc-mCherry SORTED 28.04.21 BARO -</t>
+          <t xml:space="preserve">hek 10.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR flucmCherry SORTED 28.04.21 BARO -</t>
+          <t xml:space="preserve">cal27 16.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR flucmCherry SORTED 28.04.21 BARO -</t>
+          <t xml:space="preserve">cal27 16.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR flucmCherry SORTED 28.04.21 BARO -</t>
+          <t xml:space="preserve">u2os 17.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR SIRT1 28.04.21 BARO -</t>
+          <t xml:space="preserve">hn30 20.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR SIRT1 28.04.21 BARO -</t>
+          <t xml:space="preserve">fadu 19.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 SIRT1 (retro) P81 29.03.21 BARO 81.0</t>
+          <t xml:space="preserve">hn30 20.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HeLa P31 29.03.21 BARO 31.0</t>
+          <t xml:space="preserve">hn30 11.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145-Ki PC P81 11.06.21 BARO 81.0</t>
+          <t xml:space="preserve">hek 21.0</t>
         </is>
       </c>
     </row>
@@ -870,47 +870,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+          <t xml:space="preserve">fadu 19.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+          <t xml:space="preserve">fadu 11.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+          <t xml:space="preserve">u373 21.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+          <t xml:space="preserve">fadu 19.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
+          <t xml:space="preserve">hn30 20.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #10 P19+10 07.06.21 19+10</t>
+          <t xml:space="preserve">u2os 17.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #1 P19+10 07.06.21 19+10</t>
+          <t xml:space="preserve">hek mpg ox 5.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #3 P19+10 07.06.21 19+10</t>
+          <t xml:space="preserve">mda mpg ox 9.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #12 P19+10 07.06.21 19+10</t>
+          <t xml:space="preserve">mda mpg ox 8.0</t>
         </is>
       </c>
     </row>
@@ -922,47 +922,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #9 P19+10 07.06.21 19+10</t>
+          <t xml:space="preserve">u2os mpg ox 8.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-10CR P106 13.07.21 106.0</t>
+          <t xml:space="preserve">hek mpg ox 7.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-10CR P106 13.07.21 106.0</t>
+          <t xml:space="preserve">hek mpg ox 7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P24 26.12.19 24.0</t>
+          <t xml:space="preserve">u2os mpg ox 8.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21 99.0</t>
+          <t xml:space="preserve">hek mpg ox 7.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P24 26.12.19 24.0</t>
+          <t xml:space="preserve">mda mpg ox 8.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22 134.0</t>
+          <t xml:space="preserve">u2os mpg ox 8.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21 99.0</t>
+          <t xml:space="preserve">mda mpg ox 8.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P84 12.07.21 BARO 84.0</t>
+          <t xml:space="preserve">u2os mpg ox 8.0</t>
         </is>
       </c>
     </row>
@@ -974,47 +974,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P40 29.04.22 BARO 40.0</t>
+          <t xml:space="preserve">u2os dox nek2 10.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P45 04.10.21 BARO 45.0</t>
+          <t xml:space="preserve">hek nek2 ox 4.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-CR 1x15uM recovered P110 19.08.21 BARO 110.0</t>
+          <t xml:space="preserve">hek nek2 ox 3.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-1x15CR P111 19.08.21 111.0</t>
+          <t xml:space="preserve">u2os nek2 ko b9</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2x15CR P112 13.09.21 112.0</t>
+          <t xml:space="preserve">u2os nek2 k37r 16.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR p134 15.04.22 134.0</t>
+          <t xml:space="preserve">u2os nek2 ko b5 2.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #11 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 k37r 2.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #31 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 k37r 16.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #32 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ko b9 2.0</t>
         </is>
       </c>
     </row>
@@ -1026,47 +1026,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #20 18.07.21 -</t>
+          <t xml:space="preserve">mda nek2 ox 3.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #25 18.07.21 -</t>
+          <t xml:space="preserve">hek nek2 ox 9.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #24 18.07.21 -</t>
+          <t xml:space="preserve">hek nek2 ox 3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #18 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #22 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #13 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #3 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #5 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #8 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
     </row>
@@ -1078,47 +1078,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #9 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #1 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #26 18.07.21 -</t>
+          <t xml:space="preserve">u2os dox nek2 8.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #29 18.07.21 -</t>
+          <t xml:space="preserve">u2os dox sh nek2 4.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #21 18.07.21 -</t>
+          <t xml:space="preserve">u2os dox nek2 8.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #34 18.07.21 -</t>
+          <t xml:space="preserve">u2os dox nek2 10.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #4 18.07.21 -</t>
+          <t xml:space="preserve">mda nek2 ox 7.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du-Ki #10 18.07.21 -</t>
+          <t xml:space="preserve">u2os nek2 ox 4.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22 BARO 134.0</t>
+          <t xml:space="preserve">hek 11.0</t>
         </is>
       </c>
     </row>
@@ -1130,47 +1130,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2x20CR P130 25.02.22 BARO 130.0</t>
+          <t xml:space="preserve">hek 11.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO 39.0</t>
+          <t xml:space="preserve">hek mtf1 ox</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO 39.0</t>
+          <t xml:space="preserve">hek mtf1 ox 200 13.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCaP P15-Canada 14.10.21 BARO 15.0</t>
+          <t xml:space="preserve">hek mtf1 ox 50 17.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+          <t xml:space="preserve">hek mtf1 ox 100 17.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+          <t xml:space="preserve">cal27 sh elk1 100 14.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+          <t xml:space="preserve">cal27 sh elf1 100 20.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-1x25CR P122 30.03.22 BARO 122.0</t>
+          <t xml:space="preserve">cal27 shgfp 100 24.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+          <t xml:space="preserve">cal27 sh creb1 100 24.0</t>
         </is>
       </c>
     </row>
@@ -1182,47 +1182,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2 PX+11 02.10.21 BARO X+11</t>
+          <t xml:space="preserve">cal27 sh klf4 100 24.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 P32 23.10.21 BARO 32.0</t>
+          <t xml:space="preserve">cal27 sh elf1 100 24.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-15CR* P122 16.12.21 BARO 122.0</t>
+          <t xml:space="preserve">hek mtf1 ox 200 19.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-luc 30.03.22 Ayça -</t>
+          <t xml:space="preserve">cal27 sh klf4 200 20.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 P32 23.10.21 BARO 32.0</t>
+          <t xml:space="preserve">cal27 sh elk1 100 20.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR-luc 30.03.22 Ayça -</t>
+          <t xml:space="preserve">cal27 sh creb1 100 20.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+          <t xml:space="preserve">cal27 shgfp 100 20.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PC3 cell pellet -</t>
+          <t xml:space="preserve">hek ki 5 33.0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PC3 cell pellet -</t>
+          <t xml:space="preserve">hek ki 8 43.0</t>
         </is>
       </c>
     </row>
@@ -1234,37 +1234,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCaP pellet -</t>
+          <t xml:space="preserve">hek gnt 7.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCaP pellet -</t>
+          <t xml:space="preserve">hek ki 8 mtf1 ox 24.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS pellet -</t>
+          <t xml:space="preserve">hek ki 8 55.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 pellet -</t>
+          <t xml:space="preserve">hek ki 8 54.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 pellet -</t>
+          <t xml:space="preserve">hek ki 6 43.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2 pellet -</t>
+          <t xml:space="preserve">hek ki 8 48.0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-231 pellet -</t>
+          <t xml:space="preserve">hek ki 5 39.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 8 43.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek ki 6 49.0</t>
         </is>
       </c>
     </row>
@@ -1278,14 +1288,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen → Rack 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box4  ·  baris  ·  73/81 full</t>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1  ·  beyzat  ·  24/81 full</t>
         </is>
       </c>
     </row>
@@ -1345,47 +1355,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P134 17.06.22 BARO 134.0</t>
+          <t xml:space="preserve">mda nek2 ox 4.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P56 07.08.20 BARO 56.0</t>
+          <t xml:space="preserve">hek nek2 ox 4.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P56 07.08.20 BARO 56.0</t>
+          <t xml:space="preserve">hek nek2 ox 5.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+3 P142 22.06.22 BARO 142.0</t>
+          <t xml:space="preserve">u2os nek2 k37r 7.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+3 P142 22.06.22 BARO 142.0</t>
+          <t xml:space="preserve">u2os nek2 k37r 2.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
+          <t xml:space="preserve">u2os nek2 ko b5 7.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P56 07.08.20 BARO 56.0</t>
+          <t xml:space="preserve">u2os nek2 ko b5 2.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P134 17.06.22 BARO 134.0</t>
+          <t xml:space="preserve">hek 8.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-50CR+1 P138 24.06.22 BARO 138.0</t>
+          <t xml:space="preserve">hek 7.0</t>
         </is>
       </c>
     </row>
@@ -1397,47 +1407,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-1x50CR P129 08.02.22 BARO 129.0</t>
+          <t xml:space="preserve">hek 8.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-15CR P118 08.02.22 BARO 118.0</t>
+          <t xml:space="preserve">mda 3.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-25CR P130 08.02.22 BARO 130.0</t>
+          <t xml:space="preserve">hek mtf1 ox 200 21.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P82 16.06.21 BARO 82.0</t>
+          <t xml:space="preserve">hek mtf1 ox 200 19.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P38 29.06.22 BARO 38.0</t>
+          <t xml:space="preserve">hek mtf1 ox 200 23.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
+          <t xml:space="preserve">hek ki 6 43.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
+          <t xml:space="preserve">hek ki 5 34.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #10 21.08.21 BARO -</t>
+          <t xml:space="preserve">hek ki 8 mtf1 ox 31.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P84 12.07.21 BARO 84.0</t>
+          <t xml:space="preserve">hek ki 8 mtf1 ox 29.0</t>
         </is>
       </c>
     </row>
@@ -1449,47 +1459,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PC3 P26 (MF) 28.10.21 BARO 26.0</t>
+          <t xml:space="preserve">hek mtf1 ko g3 c3 7.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCaP P17 (MF) 28.10.21 BARO 17.0</t>
+          <t xml:space="preserve">hek gnt 5.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PC3 P26 (MF) 28.10.21 BARO 26.0</t>
+          <t xml:space="preserve">hek mtf1 ko g3 c3 7.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 04.09.20 BARO 13.0</t>
+          <t xml:space="preserve">hek ki 8 mtf1 ox 29.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPE1 P36 12.10.21 BARO 36.0</t>
+          <t xml:space="preserve">hek gnt 5.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P51 23.10.21 BARO 51.0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">H1299 12.10.21 BARO -</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RPE1 P35 12.10.21 BARO 35.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RPE1 P35 12.10.21 BARO 35.0</t>
+          <t xml:space="preserve">hek mtf1 ko g3 c3 9.0</t>
         </is>
       </c>
     </row>
@@ -1499,51 +1494,6 @@
           <t xml:space="preserve">D</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P136 24.6.22 136.0</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-1x40CR P132 24.6.22 BARO 132.0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuoOceR-1x40CR P132 24.6.22 BARO 132.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-50CR+1 P138 24.06.22 BARO 138.0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P136 24.6.22 136.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR- flucmCherry SORTED 21.6.21 BARO -</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 fluc Ki PC P82 16.6.21 BARO 82.0</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR flucmCherry SORTED 21.6.21 BARO -</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIA-Paca2 16.6.21 BARO -</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1551,51 +1501,6 @@
           <t xml:space="preserve">E</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OSCC40 P42 04.03.22 Ayça 42.0</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-2x25CR P130 25.2.22 BARO 130.0</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-50CR P149 17.12.22 BARO 149.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BT549 P5 21.11.22 BARO 5.0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh3 17.10.22 BARO 50.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T P5 1.3.22 BARO 5.0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-40CR P140 11.09.22 BARO 140.0</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A549 P15 21.11.22 BARO 15.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-2x50CR P143 14.10.22 BARO 143.0</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1603,51 +1508,6 @@
           <t xml:space="preserve">F</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A549 P11 9.11.22 BARO 11.0</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A549 P12 3.11.22 BARO 12.0</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T P5 1.3.22 BARO 5.0</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BT549 P4 18.11.22 BARO 4.0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-40CR P139 2.09.22 BARO 139.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-40CR P138 26.08.22 BARO 138.0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #2 P46 13.12.22 BARO 46.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #11 P46 13.12.22 BARO 46.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #19 P46 13.12.22 BARO 46.0</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1655,51 +1515,6 @@
           <t xml:space="preserve">G</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P50 PRMT6 sh1 14.10.22 BARO 50.0</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #27 P46 13.12.22 BARO 46.0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #12 P46 13.12.22 BARO 46.0</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-40CR P140 11.09.22 BARO 140.0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-25CR P129 17.5.22 Ayça 129.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-1x50CR P142 28.9.22 BARO 142.0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A549 P12 9.11.22 BARO 12.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh3 13.10.22 BARO 50.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P50 PRMT6 sh3 17.10.22 BARO 50.0</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1707,61 +1522,11 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 P60 9.11.22 BARO 60.0</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-PARc P128 13.12.22 BARO 128.0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A549 P14 18.11.22 BARO 14.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDOceR-50CR P149 17.12.22 BARO 149.0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-20CR+4 P148 5.8.22 BARO 148.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-50CR P148 9.12.22 BARO 148.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-30CR P154 18.11.22 BARO 154.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hek-Ki #5 B.Altay 11.8.22 -</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hek-Ki #6 B.Altay 11.8.22 -</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hek-Ki #8 B.Altay 11.8.22 -</t>
         </is>
       </c>
     </row>
@@ -1775,14 +1540,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box5  ·  baris  ·  69/81 full</t>
+          <t xml:space="preserve">-80 Box1  ·  baris  ·  26/81 full</t>
         </is>
       </c>
     </row>
@@ -1842,47 +1607,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P6 29.12.22 BARO 6.0</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-50CR+2 P142 6.1.23 BARO 142.0</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-flucmCherry 14.7.21 BARO -</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P34 PRMT6 sh2 (1) 10.3.23 BARO 34.0</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P34 PRMT6 sh3 (1) 10.3.23 BARO 34.0</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P34 PRMT6 sh1 (2) 10.3.23 BARO 34.0</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P34 PRMT6 sh3 (2) 10.3.23 BARO 34.0</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P28 17.2.23 BARO 28.0</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-BCHE sh2 1.3.23 BARO -</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
         </is>
       </c>
     </row>
@@ -1894,47 +1659,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-30CR P162 6.3.23 BARO 162.0</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P39 shGFP 21.2.23 BARO 39.0</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-BCHE sh5 1.3.23 BARO -</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 -Ki 2nd sorted P93 no puro 24.5.21 BARO 93.0</t>
+          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO -</t>
+          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO -</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P6 29.12.22 BARO 6.0</t>
+          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P29 2.1.23 BARO 29.0</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO 25.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P130 3.2.23 BARO 130.0</t>
+          <t xml:space="preserve">Hela P25 22.12.19 BARO 25.0</t>
         </is>
       </c>
     </row>
@@ -1946,47 +1711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P126 29.12.22 BARO 126.0</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #17 P46 26.12.22 BARO 46.0</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P39 shGFP 21.2.23 BARO 39.0</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-PARc P135 26.1.23 BARO 135.0</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #8 P46 26.12.22 BARO 46.0</t>
+          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P39 1.2.23 BARO 39.0</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO 76.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-BCHE sh5 1.3.23 BARO -</t>
+          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO 76.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P28 17.2.23 BARO 28.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P34 PRMT6 sh2 (2) 10.3.23 BARO</t>
+          <t xml:space="preserve">U373 P80 27.1.20 BARO 80.0</t>
         </is>
       </c>
     </row>
@@ -1996,51 +1756,6 @@
           <t xml:space="preserve">D</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-20CR+7 P169 20.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #10 P46 26.12.22 BARO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P121 29.12.22 BARO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T P6 29.12.22 BARO</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P127 19.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P30 5.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P119 22.12.22 BARO</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #13 P46 26.12.22 BARO</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2048,51 +1763,6 @@
           <t xml:space="preserve">E</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P30 5.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-25CR P131 3.2.23 BARO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-PARc P132 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-50CR+2 P144 19.1.23</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-PARc P128 9.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 P60 9.11.22 BARO</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P61 21.2.23 BARO</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P131 7.2.23 BARO</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2100,51 +1770,6 @@
           <t xml:space="preserve">F</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P34 PRMT6 sh1 (1) 10.3.23 BARO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-BCHE sh2 1.3.23 BARO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDOceR-50CR+1 P150 6.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P56 31.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-PARc P132 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P61 21.2.23 BARO</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P55 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-50CR+1 P149 22.12.22 BARO</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2152,86 +1777,11 @@
           <t xml:space="preserve">G</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A375 P19 7.2.23 İpek</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-50CR+2 P147 7.2.23 BARO</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-50CR+2 P153 7.2.23 BARO</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-1x40CR P160 7.2.23 BARO</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 tet-PRMT1 sh2 (2) P36 7.2.23 BARO</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t xml:space="preserve">H</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P55 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-50CR+2 P144 26.1.23 BARO</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
         </is>
       </c>
     </row>
@@ -2252,14 +1802,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box6  ·  baris  ·  76/81 full</t>
+          <t xml:space="preserve">-80 Box2  ·  baris  ·  54/81 full</t>
         </is>
       </c>
     </row>
@@ -2319,37 +1869,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">U87MG P5 İpek 27.09.18</t>
+          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO 19+7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P10 27.10.20 Can</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO 19+7</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-PARc P134 19.91.23 BARO</t>
+          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO 19+7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #6 P19+10 7.6.21 BARO</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #5 15.4.22 Ayça</t>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 NT virus P33 25.02.22 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
         </is>
       </c>
     </row>
@@ -2361,47 +1921,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDOceR-PARc P129 12.1.23 BARO</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO 34.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-50CR+2 P143 12.1.23 BARO (T25'e aç)</t>
+          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO 34.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-50CR+1 P151 12.1.23 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
+          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCF7 P9 18.11.22 Büşra</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO -</t>
         </is>
       </c>
     </row>
@@ -2413,47 +1973,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 PRMT1KO virus P31 selected 15.2.22 BARO (Yağmur'dan virüs)</t>
+          <t xml:space="preserve">22CabaR 20.07.20 BARO -</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-50CR+2 P144 19.1.23 BARO</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO -</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P53 tet-PRMT1 sh2 19.1.23 BARO</t>
+          <t xml:space="preserve">22DoceR 20.07.20 BARO -</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P53 tet-PRMT1 sh2 19.1.23 BARO</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO -</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-PARc P134 19.1.23 BARO</t>
+          <t xml:space="preserve">22PAR 20.07.20 BARO -</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
+          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO 46.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 PC P34 1.3.22 BARO</t>
+          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO 79.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO 76.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
+          <t xml:space="preserve">TMZR P76 08.07.20 BARO 76.0</t>
         </is>
       </c>
     </row>
@@ -2465,42 +2025,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P46 ATP7B/KO-g3 #23 20.12.22 BARO</t>
+          <t xml:space="preserve">U373 P84 08.07.20 BARO 84.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-50CR P145 18.11.22 BARO</t>
+          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO 7.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO 52.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P14 21.11.21 BARO</t>
+          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO 52.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+6 P158 14.10.22 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO 51.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh1 19.1.23 BARO</t>
+          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO 51.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #7 P46 20.12.22 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO 51.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P11 (MF) 10.11.22 BARO</t>
+          <t xml:space="preserve">DuPAR P51 20.07.20 BARO 51.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+5 P153 11.9.22 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
         </is>
       </c>
     </row>
@@ -2512,47 +2077,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-50CR P145 18.11.22 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-40CR P139 2.9.22 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO 80.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P14 21.11.22 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO 77.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">A549 P12 3.11.22 BARO</t>
+          <t xml:space="preserve">U373 P85 10.07.20 BARO 85.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-1x30CR P148 11.9.22 BARO</t>
+          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO 29.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P81 1.3.22 BARO</t>
+          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC) 36.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P5 1.3.22 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO -</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P40 (MF) 11.09.22 BARO</t>
+          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO -</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDOceR-50CR P145 18.11.22 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
         </is>
       </c>
     </row>
@@ -2564,47 +2129,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-flucmCherry SORTED 22.3.22 BARO</t>
+          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 P50 PRMT6 sh3 14.10.22 BARO</t>
+          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO 80.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR 1x30CR P147 2.9.22 BARO</t>
+          <t xml:space="preserve">TMZR P77 10.07.20 BARO 77.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR+5 P153 11.9.22 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-20CR P137 17.5.22 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P15 29.9.22 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panc1 P10 MF 29.9.22 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 NT virus P31 selected 15.2.22 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P83 1.3.22 BARO</t>
+          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
         </is>
       </c>
     </row>
@@ -2614,51 +2179,6 @@
           <t xml:space="preserve">G</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">U373 P18 21.10.22 BARO</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-flucmCherry SORTED 22.3.22 BARO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Panc1 P13 18.11.22 BARO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-20CR+4 P148 26.8.22 BARO</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh2 17.10.22 BARO</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P50 PRMT6 sh1 17.10.22 BARO</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIAPAca2 P16 29.9.22 BARO</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-2x40CR P137 5.8.22 BARO</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-1x30CR P147 2.9.22 BARO</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2666,91 +2186,11 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">U373 P14 1.7.22 BARO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-2x30CR P152 3.10.22 BARO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-30CR P154 18.10.22 BARO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuPAR-20CR P132 22.3.22 BARO</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-40CR P140 11.9.22 BARO</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P46 ATP7B/KO-g3 PC 9.11.22 BARO</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Panc1 P18 1.7.22 BARO</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuCabaR-2x50CR P131 4.3.22 Baltay</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh1 17.10.22 BARO</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #6 P46 13.12.22 BARO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Panc1 P11 (MF) 10.11.22 BARO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #5 P46 13.12.22 BARO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DuDoceR-2.5CR P83 1.3.22 BARO</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #26 P46 26.12.22 BARO</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #14 P46 26.12.22 BARO</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 ATP7B/KO-g3 #15 P46 26.12.22 BARO</t>
         </is>
       </c>
     </row>
@@ -2764,14 +2204,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 1  ·  baris  ·  63/81 full</t>
+          <t xml:space="preserve">-80 Box3  ·  baris  ·  79/81 full</t>
         </is>
       </c>
     </row>
@@ -2831,47 +2271,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #9 P19+10 7.6.21 BARO</t>
+          <t xml:space="preserve">22PAR fluc-mCherry SORTED 28.04.21 BARO -</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-flucmCherry SORTED 20.4.21</t>
+          <t xml:space="preserve">22DoceR flucmCherry SORTED 28.04.21 BARO -</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #9 15.3.21</t>
+          <t xml:space="preserve">22CabaR flucmCherry SORTED 28.04.21 BARO -</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #1 15.3.21</t>
+          <t xml:space="preserve">DuDoceR flucmCherry SORTED 28.04.21 BARO -</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.1.21 BARO</t>
+          <t xml:space="preserve">DuDoceR SIRT1 28.04.21 BARO -</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-PARc P75 26.11.21 BARO</t>
+          <t xml:space="preserve">DuCabaR SIRT1 28.04.21 BARO -</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-15CR P130 1.2.22 BARO</t>
+          <t xml:space="preserve">Du145 SIRT1 (retro) P81 29.03.21 BARO 81.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-8CR P99 1.2.22 BARO</t>
+          <t xml:space="preserve">HeLa P31 29.03.21 BARO 31.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-25CR P130 1.2.22 BARO</t>
+          <t xml:space="preserve">Du145-Ki PC P81 11.06.21 BARO 81.0</t>
         </is>
       </c>
     </row>
@@ -2883,47 +2323,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P78 29.11.21 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-2.5CR P75 29.11.21 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P85 5.1.22 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-15CR* P121 8.12.21 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-10CR P110 13.7.21 BARO</t>
+          <t xml:space="preserve">HEK293T P9 29.03.21 BARO 9.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-15CR P122 16.12.21 BARO</t>
+          <t xml:space="preserve">HEK-Ki #10 P19+10 07.06.21 19+10</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-15CR P121 8.12.21 BARO</t>
+          <t xml:space="preserve">HEK-Ki #1 P19+10 07.06.21 19+10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR reminded P75 3.12.21 BARO</t>
+          <t xml:space="preserve">HEK-Ki #3 P19+10 07.06.21 19+10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-10CR P110 13.7.21 BARO</t>
+          <t xml:space="preserve">HEK-Ki #12 P19+10 07.06.21 19+10</t>
         </is>
       </c>
     </row>
@@ -2935,47 +2375,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-15CR P117 1.2.22 BARO</t>
+          <t xml:space="preserve">HEK-Ki #9 P19+10 07.06.21 19+10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-25CR P124 16.12.21 BARO</t>
+          <t xml:space="preserve">DuPAR-10CR P106 13.07.21 106.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-15CR P121 8.12.21 BARO</t>
+          <t xml:space="preserve">DuPAR-10CR P106 13.07.21 106.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-10CR P112 1.2.22 BARO</t>
+          <t xml:space="preserve">Panc1 P24 26.12.19 24.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-10CR P106 1.2.22 BARO</t>
+          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21 99.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P74 29.11.21 BARO</t>
+          <t xml:space="preserve">Panc1 P24 26.12.19 24.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-15CR P122 16.12.21 BARO</t>
+          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22 134.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-1.5CR P62 1.10.20 BARO</t>
+          <t xml:space="preserve">DuDoceR-8CR P99 13.07.21 99.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P61 25.9.20 BARO</t>
+          <t xml:space="preserve">DuDoceR-PARc P84 12.07.21 BARO 84.0</t>
         </is>
       </c>
     </row>
@@ -2987,47 +2427,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P56 7.8.20 BARO</t>
+          <t xml:space="preserve">Du145 P40 29.04.22 BARO 40.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #3 15.3.21 BARO</t>
+          <t xml:space="preserve">Du145 P45 04.10.21 BARO 45.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR-flucmCherry SORTED 16.4.21 BARO</t>
+          <t xml:space="preserve">DuPAR-CR 1x15uM recovered P110 19.08.21 BARO 110.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #10 15.3.21 BARO</t>
+          <t xml:space="preserve">DuCabaR-1x15CR P111 19.08.21 111.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #12 15.3.21 BARO</t>
+          <t xml:space="preserve">DuCabaR-2x15CR P112 13.09.21 112.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #9 15.3.21 BARO</t>
+          <t xml:space="preserve">DuPAR-20CR p134 15.04.22 134.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #1 P19+10 7.6.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #11 18.07.21 -</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #3 P19+10 7.6.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #31 18.07.21 -</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-flucmCherry 15.3.21 BARO (flucmCherry üretilen HEK'ler)</t>
+          <t xml:space="preserve">Du-Ki #32 18.07.21 -</t>
         </is>
       </c>
     </row>
@@ -3039,47 +2479,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 20.4.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #20 18.07.21 -</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #25 18.07.21 -</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-1.5CR P60 21.9.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #24 18.07.21 -</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P61 25.9.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #18 18.07.21 -</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #3 15.3.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #22 18.07.21 -</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #12 P19+10 7.6.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #13 18.07.21 -</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #12 15.3.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #3 18.07.21 -</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR-flucmCherry SORTED 22.4.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #5 18.07.21 -</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-1.5CR P62 1.10.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #8 18.07.21 -</t>
         </is>
       </c>
     </row>
@@ -3091,47 +2531,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR-flucmCherry SORTED 22.4.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #9 18.07.21 -</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR-flucmCherry SORTED 16.4.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #1 18.07.21 -</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P61 25.9.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #26 18.07.21 -</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR-flucmCherry SORTED 20.4.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #29 18.07.21 -</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR-flucmCherry SORTED 16.4.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #21 18.07.21 -</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #34 18.07.21 -</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #1 15.3.21 BARO</t>
+          <t xml:space="preserve">Du-Ki #4 18.07.21 -</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCF7 P3 7.11.20 BARO</t>
+          <t xml:space="preserve">Du-Ki #10 18.07.21 -</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231 (MF) P8 7.11.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-50CR P134 08.04.22 BARO 134.0</t>
         </is>
       </c>
     </row>
@@ -3143,47 +2583,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P62 1.10.20 BARO</t>
+          <t xml:space="preserve">DuPAR-2x20CR P130 25.02.22 BARO 130.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR-flucmCherry SORTED 20.04.21 BARO</t>
+          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO 39.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-flucmCherry 15.3.21 BARO (flucmCherry üretilen HEK'ler)</t>
+          <t xml:space="preserve">OSCC40 P39 15.02.22 BARO 39.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+          <t xml:space="preserve">LNCaP P15-Canada 14.10.21 BARO 15.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P60 21.9.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 20.4.21 BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK-Ki #10 P19+10 7.6.21 BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RPE P35 12.1.21 BARO</t>
+          <t xml:space="preserve">DuDoceR-1x25CR P122 30.03.22 BARO 122.0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1299 20.10.20 BARO</t>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
         </is>
       </c>
     </row>
@@ -3193,11 +2633,91 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HepG2 PX+11 02.10.21 BARO X+11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 P32 23.10.21 BARO 32.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-15CR* P122 16.12.21 BARO 122.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-luc 30.03.22 Ayça -</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 P32 23.10.21 BARO 32.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DtxR-luc 30.03.22 Ayça -</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-15CR P116 15.10.21 BARO 116.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PC3 cell pellet -</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PC3 cell pellet -</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCaP pellet -</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCaP pellet -</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U2OS pellet -</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 pellet -</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 pellet -</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HepG2 pellet -</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDA-231 pellet -</t>
         </is>
       </c>
     </row>
@@ -3211,14 +2731,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">LiqNitro 2  ·  baris  ·  75/81 full</t>
+          <t xml:space="preserve">-80 Box4  ·  baris  ·  73/81 full</t>
         </is>
       </c>
     </row>
@@ -3278,47 +2798,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-5CR P89 18.3.21 BARO</t>
+          <t xml:space="preserve">DuCabaR-PARc P134 17.06.22 BARO 134.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+          <t xml:space="preserve">DuPAR P56 07.08.20 BARO 56.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+          <t xml:space="preserve">DuDoceR P56 07.08.20 BARO 56.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P77 (FBS backup) 2.2.21 BARO</t>
+          <t xml:space="preserve">DuPAR-20CR+3 P142 22.06.22 BARO 142.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+          <t xml:space="preserve">DuPAR-20CR+3 P142 22.06.22 BARO 142.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P77 (FBS backup) 2.2.21 BARO</t>
+          <t xml:space="preserve">DuCabaR P56 07.08.20 BARO 56.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+          <t xml:space="preserve">DuCabaR-PARc P134 17.06.22 BARO 134.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-PARc of 2.5CR P74 17.2.21</t>
+          <t xml:space="preserve">DuCabaR-50CR+1 P138 24.06.22 BARO 138.0</t>
         </is>
       </c>
     </row>
@@ -3330,47 +2850,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
+          <t xml:space="preserve">DuCabaR-1x50CR P129 08.02.22 BARO 129.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
+          <t xml:space="preserve">DuDoceR-15CR P118 08.02.22 BARO 118.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
+          <t xml:space="preserve">DuCabaR-25CR P130 08.02.22 BARO 130.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
+          <t xml:space="preserve">Du145 P82 16.06.21 BARO 82.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
+          <t xml:space="preserve">Du145 P38 29.06.22 BARO 38.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-10CR P103 28.6.21</t>
+          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-10CR P105 7.7.21</t>
+          <t xml:space="preserve">DuPAR-20CR+2 P140 17.06.22 BARO 140.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-10CR P103 28.6.21</t>
+          <t xml:space="preserve">HEK-Ki #10 21.08.21 BARO -</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-PARc P86 21.6.21</t>
+          <t xml:space="preserve">DuCabaR-PARc P84 12.07.21 BARO 84.0</t>
         </is>
       </c>
     </row>
@@ -3382,47 +2902,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P82 7.7.21</t>
+          <t xml:space="preserve">PC3 P26 (MF) 28.10.21 BARO 26.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-8CR P98 7.7.21</t>
+          <t xml:space="preserve">LNCaP P17 (MF) 28.10.21 BARO 17.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-8CR P96 8.6.21</t>
+          <t xml:space="preserve">PC3 P26 (MF) 28.10.21 BARO 26.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
+          <t xml:space="preserve">U2OS P13 04.09.20 BARO 13.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-1x8CR P88 28.4.21</t>
+          <t xml:space="preserve">RPE1 P36 12.10.21 BARO 36.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
+          <t xml:space="preserve">Du145 P51 23.10.21 BARO 51.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
+          <t xml:space="preserve">H1299 12.10.21 BARO -</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
+          <t xml:space="preserve">RPE1 P35 12.10.21 BARO 35.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-5CR P73 27.1.21</t>
+          <t xml:space="preserve">RPE1 P35 12.10.21 BARO 35.0</t>
         </is>
       </c>
     </row>
@@ -3434,47 +2954,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
+          <t xml:space="preserve">DuCabaR-PARc P136 24.6.22 136.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-1.5CR P60 21.9.20</t>
+          <t xml:space="preserve">DuDoceR-1x40CR P132 24.6.22 BARO 132.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
+          <t xml:space="preserve">DuoOceR-1x40CR P132 24.6.22 BARO 132.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
+          <t xml:space="preserve">DuCabaR-50CR+1 P138 24.06.22 BARO 138.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
+          <t xml:space="preserve">DuCabaR-PARc P136 24.6.22 136.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-2.5CR P74 (FBS backup) 2.2.21</t>
+          <t xml:space="preserve">DuPAR- flucmCherry SORTED 21.6.21 BARO -</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P64 2.1.21</t>
+          <t xml:space="preserve">Du145 fluc Ki PC P82 16.6.21 BARO 82.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-2.5CR P74 (FBS backup) 2.2.21</t>
+          <t xml:space="preserve">DuDoceR flucmCherry SORTED 21.6.21 BARO -</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
+          <t xml:space="preserve">MIA-Paca2 16.6.21 BARO -</t>
         </is>
       </c>
     </row>
@@ -3486,47 +3006,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
+          <t xml:space="preserve">OSCC40 P42 04.03.22 Ayça 42.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
+          <t xml:space="preserve">DuPAR-2x25CR P130 25.2.22 BARO 130.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-1x10CR P99 28.4.21</t>
+          <t xml:space="preserve">DuDoceR-50CR P149 17.12.22 BARO 149.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
+          <t xml:space="preserve">BT549 P5 21.11.22 BARO 5.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P77 21.6.21</t>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh3 17.10.22 BARO 50.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P65 26.3.21</t>
+          <t xml:space="preserve">HEK293T P5 1.3.22 BARO 5.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+          <t xml:space="preserve">DuDoceR-40CR P140 11.09.22 BARO 140.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-10CR P105 19.6.21</t>
+          <t xml:space="preserve">A549 P15 21.11.22 BARO 15.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-10CR P109 7.7.21</t>
+          <t xml:space="preserve">DuDoceR-2x50CR P143 14.10.22 BARO 143.0</t>
         </is>
       </c>
     </row>
@@ -3538,47 +3058,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-1.5CR P62 1.10.20</t>
+          <t xml:space="preserve">A549 P11 9.11.22 BARO 11.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR-PARc P90 7.7.21</t>
+          <t xml:space="preserve">A549 P12 3.11.22 BARO 12.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+          <t xml:space="preserve">HEK293T P5 1.3.22 BARO 5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+          <t xml:space="preserve">BT549 P4 18.11.22 BARO 4.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+          <t xml:space="preserve">DuDoceR-40CR P139 2.09.22 BARO 139.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-1.5CR P62 1.10.20</t>
+          <t xml:space="preserve">DuDoceR-40CR P138 26.08.22 BARO 138.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #2 P46 13.12.22 BARO 46.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #11 P46 13.12.22 BARO 46.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #19 P46 13.12.22 BARO 46.0</t>
         </is>
       </c>
     </row>
@@ -3590,37 +3110,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
+          <t xml:space="preserve">Du145 P50 PRMT6 sh1 14.10.22 BARO 50.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P62 1.10.20</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #27 P46 13.12.22 BARO 46.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P61 25.9.20</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #12 P46 13.12.22 BARO 46.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+          <t xml:space="preserve">DuDoceR-40CR P140 11.09.22 BARO 140.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-2.5CR P81 (FBS backup) 2.2.21</t>
+          <t xml:space="preserve">DuDoceR-25CR P129 17.5.22 Ayça 129.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+          <t xml:space="preserve">DuDoceR-1x50CR P142 28.9.22 BARO 142.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+          <t xml:space="preserve">A549 P12 9.11.22 BARO 12.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh3 13.10.22 BARO 50.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 PRMT6 sh3 17.10.22 BARO 50.0</t>
         </is>
       </c>
     </row>
@@ -3630,34 +3160,49 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 P60 9.11.22 BARO 60.0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-PARc P128 13.12.22 BARO 128.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A549 P14 18.11.22 BARO 14.0</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 shGFP puro 51.0</t>
+          <t xml:space="preserve">DuDOceR-50CR P149 17.12.22 BARO 149.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSC19 TMEM16 OX p+17</t>
+          <t xml:space="preserve">DuPAR-20CR+4 P148 5.8.22 BARO 148.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSC19 Empty Vector P+18</t>
+          <t xml:space="preserve">DuDoceR-50CR P148 9.12.22 BARO 148.0</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR PARc 137.0</t>
+          <t xml:space="preserve">DuPAR-30CR P154 18.11.22 BARO 154.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR PARc 137.0</t>
+          <t xml:space="preserve">Hek-Ki #5 B.Altay 11.8.22 -</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 shGFP hygro 200 ul 42.0</t>
+          <t xml:space="preserve">Hek-Ki #6 B.Altay 11.8.22 -</t>
         </is>
       </c>
     </row>
@@ -3669,42 +3214,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 tet PRMT1 sh2(2) puro 49.0</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK Knock In #6 41.0</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK Knock In #6 41.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK Knock In #5 31.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK Knock In #5 31.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK Knock In #5 29.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK Knock In #5 29.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK Knock In #5 40.0</t>
+          <t xml:space="preserve">Hek-Ki #8 B.Altay 11.8.22 -</t>
         </is>
       </c>
     </row>
@@ -3718,14 +3228,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Hücre Box 1  ·  beyzat  ·  81/81 full</t>
+          <t xml:space="preserve">-80 Box5  ·  baris  ·  69/81 full</t>
         </is>
       </c>
     </row>
@@ -3785,47 +3295,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 10.0</t>
+          <t xml:space="preserve">HEK293T P6 29.12.22 BARO 6.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 16.0</t>
+          <t xml:space="preserve">DuCabaR-50CR+2 P142 6.1.23 BARO 142.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 16.0</t>
+          <t xml:space="preserve">DuDoceR-flucmCherry 14.7.21 BARO -</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os 17.0</t>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh2 (1) 10.3.23 BARO 34.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hn30 20.0</t>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh3 (1) 10.3.23 BARO 34.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fadu 19.0</t>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh1 (2) 10.3.23 BARO 34.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hn30 20.0</t>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh3 (2) 10.3.23 BARO 34.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hn30 11.0</t>
+          <t xml:space="preserve">Du145 P28 17.2.23 BARO 28.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 21.0</t>
+          <t xml:space="preserve">DuPAR-BCHE sh2 1.3.23 BARO -</t>
         </is>
       </c>
     </row>
@@ -3837,47 +3347,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fadu 19.0</t>
+          <t xml:space="preserve">DuPAR-30CR P162 6.3.23 BARO 162.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fadu 11.0</t>
+          <t xml:space="preserve">Du145 P39 shGFP 21.2.23 BARO 39.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">u373 21.0</t>
+          <t xml:space="preserve">DuPAR-BCHE sh5 1.3.23 BARO -</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fadu 19.0</t>
+          <t xml:space="preserve">Du145 -Ki 2nd sorted P93 no puro 24.5.21 BARO 93.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hn30 20.0</t>
+          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO -</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os 17.0</t>
+          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO -</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox 5.0</t>
+          <t xml:space="preserve">HEK293T P6 29.12.22 BARO 6.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox 9.0</t>
+          <t xml:space="preserve">Du145 P29 2.1.23 BARO 29.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox 8.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P130 3.2.23 BARO 130.0</t>
         </is>
       </c>
     </row>
@@ -3889,47 +3399,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os mpg ox 8.0</t>
+          <t xml:space="preserve">DuDoceR-PARc P126 29.12.22 BARO 126.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox 7.0</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #17 P46 26.12.22 BARO 46.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox 7.0</t>
+          <t xml:space="preserve">Du145 P39 shGFP 21.2.23 BARO 39.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os mpg ox 8.0</t>
+          <t xml:space="preserve">DuPAR-PARc P135 26.1.23 BARO 135.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mpg ox 7.0</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #8 P46 26.12.22 BARO 46.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox 8.0</t>
+          <t xml:space="preserve">Du145 P39 1.2.23 BARO 39.0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os mpg ox 8.0</t>
+          <t xml:space="preserve">DuPAR-BCHE sh5 1.3.23 BARO -</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda mpg ox 8.0</t>
+          <t xml:space="preserve">Du145 P28 17.2.23 BARO 28.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os mpg ox 8.0</t>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh2 (2) 10.3.23 BARO</t>
         </is>
       </c>
     </row>
@@ -3941,47 +3451,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2 10.0</t>
+          <t xml:space="preserve">DuPAR-20CR+7 P169 20.1.23 BARO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox 4.0</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #10 P46 26.12.22 BARO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox 3.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P121 29.12.22 BARO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ko b9</t>
+          <t xml:space="preserve">HEK293T P6 29.12.22 BARO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 k37r 16.0</t>
+          <t xml:space="preserve">DuPAR-flucmCherry 14.7.21 BARO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ko b5 2.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P127 19.1.23 BARO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 k37r 2.0</t>
+          <t xml:space="preserve">Du145 P30 5.1.23 BARO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 k37r 16.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P119 22.12.22 BARO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ko b9 2.0</t>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #13 P46 26.12.22 BARO</t>
         </is>
       </c>
     </row>
@@ -3993,47 +3503,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox 3.0</t>
+          <t xml:space="preserve">Du145 P30 5.1.23 BARO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox 9.0</t>
+          <t xml:space="preserve">DuDoceR-25CR P131 3.2.23 BARO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox 3.0</t>
+          <t xml:space="preserve">DuDoceR-PARc P132 26.1.23 BARO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">DuCabaR-50CR+2 P144 19.1.23</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">DuDoceR-PARc P128 9.1.23 BARO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">Huh7 P60 9.11.22 BARO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P61 21.2.23 BARO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P131 7.2.23 BARO</t>
         </is>
       </c>
     </row>
@@ -4045,47 +3555,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">Du145 P34 PRMT6 sh1 (1) 10.3.23 BARO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">DuPAR-BCHE sh2 1.3.23 BARO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2 8.0</t>
+          <t xml:space="preserve">DuDOceR-50CR+1 P150 6.1.23 BARO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox sh nek2 4.0</t>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P56 31.1.23 BARO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2 8.0</t>
+          <t xml:space="preserve">DuDoceR-PARc P132 26.1.23 BARO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os dox nek2 10.0</t>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P61 21.2.23 BARO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox 7.0</t>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P55 26.1.23 BARO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ox 4.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 11.0</t>
+          <t xml:space="preserve">DuDoceR-50CR+1 P149 22.12.22 BARO</t>
         </is>
       </c>
     </row>
@@ -4097,47 +3607,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 11.0</t>
+          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox</t>
+          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 200 13.0</t>
+          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 50 17.0</t>
+          <t xml:space="preserve">DuPAR-30CR+1 P163 22.3.23 BARO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 100 17.0</t>
+          <t xml:space="preserve">A375 P19 7.2.23 İpek</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh elk1 100 14.0</t>
+          <t xml:space="preserve">DuCabaR-50CR+2 P147 7.2.23 BARO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh elf1 100 20.0</t>
+          <t xml:space="preserve">DuDoceR-50CR+2 P153 7.2.23 BARO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 shgfp 100 24.0</t>
+          <t xml:space="preserve">DuPAR-1x40CR P160 7.2.23 BARO</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh creb1 100 24.0</t>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 (2) P36 7.2.23 BARO</t>
         </is>
       </c>
     </row>
@@ -4149,47 +3659,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh klf4 100 24.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P128 26.1.23 BARO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh elf1 100 24.0</t>
+          <t xml:space="preserve">Du145 tet-PRMT1 sh2 P55 26.1.23 BARO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 200 19.0</t>
+          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh klf4 200 20.0</t>
+          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh elk1 100 20.0</t>
+          <t xml:space="preserve">DuCabaR-50CR+2 P144 26.1.23 BARO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cal27 sh creb1 100 20.0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cal27 shgfp 100 20.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 5 33.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 8 43.0</t>
+          <t xml:space="preserve">DuDoceR-50CR+1 P153 26.1.23 BARO</t>
         </is>
       </c>
     </row>
@@ -4197,51 +3692,6 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek gnt 7.0</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 8 mtf1 ox 24.0</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 8 55.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 8 54.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 6 43.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 8 48.0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 5 39.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 8 43.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek ki 6 49.0</t>
         </is>
       </c>
     </row>
@@ -4255,14 +3705,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Baris Shelf</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1  ·  beyzat  ·  24/81 full</t>
+          <t xml:space="preserve">-80 Box6  ·  baris  ·  76/81 full</t>
         </is>
       </c>
     </row>
@@ -4322,47 +3772,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda nek2 ox 4.0</t>
+          <t xml:space="preserve">U87MG P5 İpek 27.09.18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox 4.0</t>
+          <t xml:space="preserve">Panc1 P10 27.10.20 Can</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek nek2 ox 5.0</t>
+          <t xml:space="preserve">DuPAR-PARc P134 19.91.23 BARO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 k37r 7.0</t>
+          <t xml:space="preserve">HEK-Ki #6 P19+10 7.6.21 BARO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 k37r 2.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">u2os nek2 ko b5 7.0</t>
+          <t xml:space="preserve">HEK-Ki #5 15.4.22 Ayça</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">u2os nek2 ko b5 2.0</t>
+          <t xml:space="preserve">Du145 NT virus P33 25.02.22 BARO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 8.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hek 7.0</t>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
         </is>
       </c>
     </row>
@@ -4374,47 +3814,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 8.0</t>
+          <t xml:space="preserve">DuDOceR-PARc P129 12.1.23 BARO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mda 3.0</t>
+          <t xml:space="preserve">DuCabaR-50CR+2 P143 12.1.23 BARO (T25'e aç)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 200 21.0</t>
+          <t xml:space="preserve">DuDoceR-50CR+1 P151 12.1.23 BARO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 200 19.0</t>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ox 200 23.0</t>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 6 43.0</t>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 5 34.0</t>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8 mtf1 ox 31.0</t>
+          <t xml:space="preserve">HEK293T P10 11.01.23 BARO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8 mtf1 ox 29.0</t>
+          <t xml:space="preserve">MCF7 P9 18.11.22 Büşra</t>
         </is>
       </c>
     </row>
@@ -4426,32 +3866,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ko g3 c3 7.0</t>
+          <t xml:space="preserve">Du145 PRMT1KO virus P31 selected 15.2.22 BARO (Yağmur'dan virüs)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek gnt 5.0</t>
+          <t xml:space="preserve">DuCabaR-50CR+2 P144 19.1.23 BARO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ko g3 c3 7.0</t>
+          <t xml:space="preserve">Du145 P53 tet-PRMT1 sh2 19.1.23 BARO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek ki 8 mtf1 ox 29.0</t>
+          <t xml:space="preserve">Du145 P53 tet-PRMT1 sh2 19.1.23 BARO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek gnt 5.0</t>
+          <t xml:space="preserve">DuPAR-PARc P134 19.1.23 BARO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek mtf1 ko g3 c3 9.0</t>
+          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 PC P34 1.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+7 P168 19.1.23 BARO</t>
         </is>
       </c>
     </row>
@@ -4461,6 +3916,46 @@
           <t xml:space="preserve">D</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P46 ATP7B/KO-g3 #23 20.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR P145 18.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P14 21.11.21 BARO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+6 P158 14.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh1 19.1.23 BARO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #7 P46 20.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P11 (MF) 10.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+5 P153 11.9.22 BARO</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4468,6 +3963,51 @@
           <t xml:space="preserve">E</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-50CR P145 18.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-40CR P139 2.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P14 21.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A549 P12 3.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-1x30CR P148 11.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P81 1.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T P5 1.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P40 (MF) 11.09.22 BARO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDOceR-50CR P145 18.11.22 BARO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4475,6 +4015,51 @@
           <t xml:space="preserve">F</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-flucmCherry SORTED 22.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 PRMT6 sh3 14.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR 1x30CR P147 2.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+5 P153 11.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR P137 17.5.22 BARO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P15 29.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P10 MF 29.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 NT virus P31 selected 15.2.22 BARO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2.5CR P83 1.3.22 BARO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4482,6 +4067,51 @@
           <t xml:space="preserve">G</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P18 21.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-flucmCherry SORTED 22.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P13 18.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR+4 P148 26.8.22 BARO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh2 17.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 PRMT6 sh1 17.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIAPAca2 P16 29.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2x40CR P137 5.8.22 BARO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-1x30CR P147 2.9.22 BARO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4489,11 +4119,91 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">U373 P14 1.7.22 BARO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-2x30CR P152 3.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-30CR P154 18.10.22 BARO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR-20CR P132 22.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-40CR P140 11.9.22 BARO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P46 ATP7B/KO-g3 PC 9.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P18 1.7.22 BARO</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2x50CR P131 4.3.22 Baltay</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 P50 tet-PRMT1 sh1 17.10.22 BARO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #6 P46 13.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Panc1 P11 (MF) 10.11.22 BARO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #5 P46 13.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-2.5CR P83 1.3.22 BARO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #26 P46 26.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #14 P46 26.12.22 BARO</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 ATP7B/KO-g3 #15 P46 26.12.22 BARO</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 2 → Beyza Shelf</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6292,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ONGOING  ·  umut  ·  76/81 full</t>
+          <t xml:space="preserve">ONGOING  ·  umut  ·  75/81 full</t>
         </is>
       </c>
     </row>
@@ -6896,11 +6606,6 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145 p?</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145 p?</t>
         </is>
@@ -7094,7 +6799,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  42/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  56/81 full</t>
         </is>
       </c>
     </row>
@@ -7389,6 +7094,31 @@
           <t xml:space="preserve">LNCX p+24</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP1 p+24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP1 p+24</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP2 p+24</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP2 p+24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP3 p+24</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7398,7 +7128,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LUCX p21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7416,6 +7146,51 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP3 p+24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC1 p+24</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC1 p+24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC2 p+24</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC2 p+24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC3 p+24</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC3 p+24</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC4 p+24</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC4 p+24</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7204,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2</t>
         </is>
       </c>
     </row>
@@ -7561,14 +7336,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box1  ·  baris  ·  26/81 full</t>
+          <t xml:space="preserve">LiqNitro 1  ·  baris  ·  63/81 full</t>
         </is>
       </c>
     </row>
@@ -7628,47 +7403,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+          <t xml:space="preserve">HEK-Ki #9 P19+10 7.6.21 BARO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+          <t xml:space="preserve">DuPAR-flucmCherry SORTED 20.4.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+          <t xml:space="preserve">HEK-Ki #9 15.3.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+          <t xml:space="preserve">HEK-Ki #1 15.3.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.1.21 BARO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuPAR-PARc P75 26.11.21 BARO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuPAR-15CR P130 1.2.22 BARO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuDoceR-8CR P99 1.2.22 BARO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuCabaR-25CR P130 1.2.22 BARO</t>
         </is>
       </c>
     </row>
@@ -7680,47 +7455,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuCabaR-2.5CR P78 29.11.21 BARO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuDoceR-2.5CR P75 29.11.21 BARO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuCabaR-2.5CR P85 5.1.22 BARO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 14.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuPAR-15CR* P121 8.12.21 BARO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P23 15.12.19 BARO 23.0</t>
+          <t xml:space="preserve">DuCabaR-10CR P110 13.7.21 BARO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+          <t xml:space="preserve">DuPAR-15CR P122 16.12.21 BARO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 10.02.20 BARO 24.0</t>
+          <t xml:space="preserve">DuPAR-15CR P121 8.12.21 BARO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO 25.0</t>
+          <t xml:space="preserve">DuPAR-2.5CR reminded P75 3.12.21 BARO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P25 22.12.19 BARO 25.0</t>
+          <t xml:space="preserve">DuCabaR-10CR P110 13.7.21 BARO</t>
         </is>
       </c>
     </row>
@@ -7732,42 +7507,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+          <t xml:space="preserve">DuDoceR-15CR P117 1.2.22 BARO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+          <t xml:space="preserve">DuCabaR-25CR P124 16.12.21 BARO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+          <t xml:space="preserve">DuPAR-15CR P121 8.12.21 BARO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+          <t xml:space="preserve">DuCabaR-10CR P112 1.2.22 BARO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela P24 1.1.20 BARO 24.0</t>
+          <t xml:space="preserve">DuPAR-10CR P106 1.2.22 BARO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO 76.0</t>
+          <t xml:space="preserve">DuPAR-2.5CR P74 29.11.21 BARO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P76 27.01.20 BARO 76.0</t>
+          <t xml:space="preserve">DuPAR-15CR P122 16.12.21 BARO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P80 27.1.20 BARO 80.0</t>
+          <t xml:space="preserve">DuDoceR-1.5CR P62 1.10.20 BARO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P61 25.9.20 BARO</t>
         </is>
       </c>
     </row>
@@ -7777,6 +7557,51 @@
           <t xml:space="preserve">D</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR P56 7.8.20 BARO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #3 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #10 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #12 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #9 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #1 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #3 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-flucmCherry 15.3.21 BARO (flucmCherry üretilen HEK'ler)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7784,6 +7609,51 @@
           <t xml:space="preserve">E</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 20.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-1.5CR P60 21.9.20 BARO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P61 25.9.20 BARO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #3 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #12 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #12 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22CabaR-flucmCherry SORTED 22.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-1.5CR P62 1.10.20 BARO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -7791,11 +7661,101 @@
           <t xml:space="preserve">F</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22DoceR-flucmCherry SORTED 22.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P61 25.9.20 BARO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR-flucmCherry SORTED 20.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22DoceR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #1 15.3.21 BARO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MCF7 P3 7.11.20 BARO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDA-MB-231 (MF) P8 7.11.20 BARO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDoceR-PARc P62 1.10.20 BARO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22PAR-flucmCherry SORTED 20.04.21 BARO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-flucmCherry 15.3.21 BARO (flucmCherry üretilen HEK'ler)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 16.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P60 21.9.20 BARO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-flucmCherry SORTED 20.4.21 BARO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK-Ki #10 P19+10 7.6.21 BARO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RPE P35 12.1.21 BARO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H1299 20.10.20 BARO</t>
         </is>
       </c>
     </row>
@@ -7823,14 +7783,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Liquid Nitrogen → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">-80 Box2  ·  baris  ·  54/81 full</t>
+          <t xml:space="preserve">LiqNitro 2  ·  baris  ·  75/81 full</t>
         </is>
       </c>
     </row>
@@ -7890,47 +7850,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T-Ki-g1,3 P19+7 17.12.20 BARO 19+7</t>
+          <t xml:space="preserve">DuPAR-5CR P89 18.3.21 BARO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO 19+7</t>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK Ki-g1,3 P19+7 17.02.20 BARO 19+7</t>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
+          <t xml:space="preserve">DuPAR-2.5CR P77 (FBS backup) 2.2.21 BARO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T Ki-g1 P19+7 17.12.20 BARO 19+7</t>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
+          <t xml:space="preserve">DuPAR-2.5CR P77 (FBS backup) 2.2.21 BARO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2OS P13 4.9.20 BARO 13.0</t>
+          <t xml:space="preserve">DuPAR-PARc of 2.5CR P74 17.2.21</t>
         </is>
       </c>
     </row>
@@ -7942,47 +7902,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO 34.0</t>
+          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 4RC P34 06.08.20 BARO 34.0</t>
+          <t xml:space="preserve">DuPAR-2.5CR P72 13.1.21 BARO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
+          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
+          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P55 01.08.20 BARO 55.0</t>
+          <t xml:space="preserve">DuPAR-5CR P88 15.3.21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
+          <t xml:space="preserve">DuPAR-10CR P103 28.6.21</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
+          <t xml:space="preserve">DuPAR-10CR P105 7.7.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P55 01.08.20 BARO 55.0</t>
+          <t xml:space="preserve">DuPAR-10CR P103 28.6.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO -</t>
+          <t xml:space="preserve">DuPAR-PARc P86 21.6.21</t>
         </is>
       </c>
     </row>
@@ -7994,47 +7954,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">22CabaR 20.07.20 BARO -</t>
+          <t xml:space="preserve">DuDoceR-PARc P82 7.7.21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO -</t>
+          <t xml:space="preserve">DuDoceR-8CR P98 7.7.21</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">22DoceR 20.07.20 BARO -</t>
+          <t xml:space="preserve">DuDoceR-8CR P96 8.6.21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO -</t>
+          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">22PAR 20.07.20 BARO -</t>
+          <t xml:space="preserve">DuDoceR-1x8CR P88 28.4.21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P46 16.07.20 BARO 46.0</t>
+          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P79 08.07.20 BARO 79.0</t>
+          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO 76.0</t>
+          <t xml:space="preserve">DuDoceR-4CR P82 18.3.21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P76 08.07.20 BARO 76.0</t>
+          <t xml:space="preserve">DuDoceR-5CR P73 27.1.21</t>
         </is>
       </c>
     </row>
@@ -8046,47 +8006,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P84 08.07.20 BARO 84.0</t>
+          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuramochi P7 (R10) 31.07.20 BARO 7.0</t>
+          <t xml:space="preserve">DuDoceR-1.5CR P60 21.9.20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO 52.0</t>
+          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuCabaR P52 20.07.20 BARO 52.0</t>
+          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO 51.0</t>
+          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDoceR P51 20.07.20 BARO 51.0</t>
+          <t xml:space="preserve">DuDoceR-2.5CR P74 (FBS backup) 2.2.21</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO 51.0</t>
+          <t xml:space="preserve">DuDoceR-PARc P64 2.1.21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPAR P51 20.07.20 BARO 51.0</t>
+          <t xml:space="preserve">DuDoceR-2.5CR P74 (FBS backup) 2.2.21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
+          <t xml:space="preserve">DuDoceR-2.5CR P73 27.1.21</t>
         </is>
       </c>
     </row>
@@ -8098,47 +8058,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
+          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO 80.0</t>
+          <t xml:space="preserve">DuDoceR-PARc P64 12.1.21</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO 77.0</t>
+          <t xml:space="preserve">DuCabaR-1x10CR P99 28.4.21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">U373 P85 10.07.20 BARO 85.0</t>
+          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela 2CR P29 17.02.20 BARO 29.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P77 21.6.21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hela PARc P36 17.02.20 BARO (PARc of 2RC) 36.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P65 26.3.21</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO -</t>
+          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">22Rv1 CabaR 13.03.20 BARO -</t>
+          <t xml:space="preserve">DuCabaR-10CR P105 19.6.21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
+          <t xml:space="preserve">DuCabaR-10CR P109 7.7.21</t>
         </is>
       </c>
     </row>
@@ -8150,47 +8110,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2780 P49 14.07.20(?) BARO 49.0</t>
+          <t xml:space="preserve">DuCabaR-1.5CR P62 1.10.20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE-TMZR P80 10.07.20 BARO 80.0</t>
+          <t xml:space="preserve">DuPAR-PARc P90 7.7.21</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TMZR P77 10.07.20 BARO 77.0</t>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+          <t xml:space="preserve">DuCabaR-1.5CR P62 1.10.20</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T P9 02.03.20 BARO 9.0</t>
+          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
         </is>
       </c>
     </row>
@@ -8200,6 +8160,41 @@
           <t xml:space="preserve">G</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-5CR P92 18.3.21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P62 1.10.20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P61 25.9.20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P76 13.1.21</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-2.5CR P81 (FBS backup) 2.2.21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuCabaR-PARc P64 12.1.21</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8207,11 +8202,81 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 shGFP puro 51.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSC19 TMEM16 OX p+17</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OSC19 Empty Vector P+18</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR PARc 137.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPAR PARc 137.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 shGFP hygro 200 ul 42.0</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145 tet PRMT1 sh2(2) puro 49.0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #6 41.0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #6 41.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 31.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 31.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 29.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 29.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK Knock In #5 40.0</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -214,13 +214,13 @@
         <v>9</v>
       </c>
       <c r="G4">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H4">
         <v>81</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -288,13 +288,13 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H6">
         <v>81</v>
       </c>
       <c r="I6">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -5780,7 +5780,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE  ·  umut  ·  76/81 full</t>
+          <t xml:space="preserve">DUZENLE  ·  umut  ·  79/81 full</t>
         </is>
       </c>
     </row>
@@ -6071,9 +6071,19 @@
           <t xml:space="preserve">Huh7 ATF3 OX rep2 p14</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 gNT p19</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7 gNT p17</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3 p19</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -6267,6 +6277,11 @@
       <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK ATP7B KO g3 p+2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT p23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -6799,7 +6814,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  56/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  61/81 full</t>
         </is>
       </c>
     </row>
@@ -6872,9 +6887,19 @@
           <t xml:space="preserve">HEK gNT p27</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 3xFLAG p22</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK ATF3 KO rep2 p21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 OX rep3 p29</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6929,6 +6954,11 @@
           <t xml:space="preserve">HEK293T p14</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2 p26</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK gNT p21</t>
@@ -7003,9 +7033,19 @@
           <t xml:space="preserve">Huh7 p15</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 3xFLAG p19</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7 3xFLAG p17</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3 p19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -671,13 +671,13 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H15">
         <v>81</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -751,13 +751,13 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H17">
         <v>81</v>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>81</v>
       </c>
       <c r="J19">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -880,7 +880,7 @@
         <v>81</v>
       </c>
       <c r="J20">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -920,7 +920,7 @@
         <v>81</v>
       </c>
       <c r="J21">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -960,7 +960,7 @@
         <v>81</v>
       </c>
       <c r="J22">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1000,7 +1000,7 @@
         <v>81</v>
       </c>
       <c r="J23">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1040,7 +1040,7 @@
         <v>81</v>
       </c>
       <c r="J24">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3605,7 +3605,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DUZENLE  ·  umut  ·  79/81 full</t>
+          <t xml:space="preserve">DUZENLE  ·  umut  ·  81/81 full</t>
         </is>
       </c>
     </row>
@@ -4060,6 +4060,16 @@
       <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">LUCX p19</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP1 23</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP3 23</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4649,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  61/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  64/81 full</t>
         </is>
       </c>
     </row>
@@ -5004,6 +5014,21 @@
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">LUCX p21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gC2 23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gC3 23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gC4 23</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5233,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box  ·  umut  ·  0/81 full + 14 without a slot</t>
+          <t xml:space="preserve">ChIP Box  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -5320,112 +5345,6 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In this box, no slot recorded (14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region 1_F  GTCTCGGCCACCTCG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region 1_R  CAGAGCGGACCCGAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region 2_F  TCAATCACAGGCCACGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region 2_R  GGGCCAATTGTGCGTTAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region3_F  TACTTGCCCGTCCAGTGTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region3_R  AGCAGAAGAAAACGCGGTAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region4_F  ACGATTGAGCCACGAGACAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region4_R  AAAAAGCAGAGGATTCAACATAAGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region5_F  GCCCTCCACTAATAAAACAGAAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region5_R  GACAAAAACGAAGAAGAAATGCCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region6_F  ACTGTCCTCTGTAGTGTTGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region6_R  TTGAGGATCCATTGAAGGGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region7_F  TGTGGTCTAGCATCAGAGAAGAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Region7_R  CCAGATAGTGGCTCCTCCTTTC</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5812,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-  ·  umut  ·  0/81 full + 38 without a slot</t>
+          <t xml:space="preserve">ChIP Box -2-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6005,280 +5924,6 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In this box, no slot recorded (38)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC1_F  caccgAGCCCCCCCAAATCATTTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC1_R  aaacCTAAATGATTTGGGGGGGCTc</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC2_F  caccgGGAAGGATAGTGAACCATCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC2_R  aaacGGATGGTTCACTATCCTTCCc</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC3_F  caccgCCACAAACTTGTACCTTGGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC3_R  aaacTCCAAGGTACAAGTTTGTGGc</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC4_F  caccgACTGCCTCTAAATGATTTGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC4_R  aaacCCAAATCATTTAGAGGCAGTc</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gP1_F  caccgGGCTCCCCGGGATCTCGGAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gP1_R  aaacCTCCGAGATCCCGGGGAGCCc</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gP2_F  caccgCTGGCTCCCCGGGATCTCGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gP2_R  aaacCCGAGATCCCGGGGAGCCAGc</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gP3_F  caccgAGTGCTGTACAGGAGCCGAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gP3_R  aaacTTCGGCTCCTGTACAGCACTc</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gP4_F  caccgGCTCCTGTACAGCACTGGAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gP4_R  aaacCTCCAGTGCTGTACAGGAGCc</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_F  CCAACATCAAATAACATCAAGGAAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_F_2  GGCAGTGATCTGCCACAAAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_F1  GGCAGTGATCTGCCACAAAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_F2  CCACCTCTGTGCCCTTCATT</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_F3  GGCCCATTCTCTAGCCCTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_F4  TCTGAATGCAGCCAAAACCAAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_F5  AACTCTCTGAATGCAGCCAAAAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_R  TGGTGTATTCTGTTCACACTGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_R_2  ACTGCAGGGCTAGAGAATGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_R1  ACTGCAGGGCTAGAGAATGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_R2  TGGGCCTGGATGGTTCACTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_R3  CAGAAACAGTCTTTGCCGCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_R4  GGCAGGGGAAAAATTGTGGTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_C3_R5  AGGCAGGGGAAAAATTGTGGTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_P_F1  CTGTTGCATTTGCTCTCCAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_P_F2  CCCGACTCGCAAACTGTTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_P_R1  CGGCTAGCTCGGCCCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_P_R2  TACAGCACTGGAGCGGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_P2_F  CAAACTGTTGCATTTGCTCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_P2_F2  CGACTCGCAAACTGTTGCAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_P2_R  CCTCTGGGCTTGCTCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ChIP_AR_P2_R2  TTTTTCCCTCTGTCGCCTCC</t>
         </is>
       </c>
     </row>
@@ -6299,7 +5944,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-  ·  umut  ·  0/81 full + 22 without a slot</t>
+          <t xml:space="preserve">Umut -20 -2-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6411,168 +6056,6 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In this box, no slot recorded (22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR45_qPCR_F  AGAGGGATTCCTCGGAGGTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR45_qPCR_R  GGCAATGTCAGGAGCACTCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3_qPCR_F  GCCATCACAGCAGGTTTCCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3_qPCR_R  TTTGCTAAGGAATGGCCCGC</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FOXC1_F  CAGTCTCTGTACCGCACGTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FOXC1_R  TTCGGCTTTGAGGGTGTGTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pac1_ZNF24  cccTTAATTAAatgtctgcacagtcagtgga</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3_qPCR_F  GGAGAAACGGACCAAGGAGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3_qPCR_R  CGAGATCTCATGATCGCCCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1_qPCR_F  AGAGGAACGACACCAGGAGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1_qPCR_R  CCTCTGCCTGTGCAATCTCA</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1_qPCR_F  TAGTGGAGTGGAAGCGGAGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1_qPCR_R  TCTGCAGCTGATCCAAGCAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Xba1_YY1  aaaTCTAGAatggcctcgggcgacaccct</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">YY1_BamH1  cccGGATCCctggttgtttttggccttag</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZNF24_g1_F  CACCttggataccaggattcacct</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZNF24_g1_R  AAACaggtgaatcctggtatccaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZNF24_g2_F  CACCcttcatcaaagaattcacag</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZNF24_g2_R  AAACctgtgaattctttgatgaag</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZNF24_Not1  aaaGCGGCCGCaactttcacaac</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZNF24_qPCR_F  AGCCGGAGGTTTGCGCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ZNF24_qPCR_R  TGAGGCAGAATATAAGCCTCAGGG</t>
         </is>
       </c>
     </row>
@@ -6593,7 +6076,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-  ·  umut  ·  0/81 full + 46 without a slot</t>
+          <t xml:space="preserve">Umut -20 Box -1-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6705,336 +6188,6 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In this box, no slot recorded (46)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">APEX1-g1-F  caccgGATCAGAAAACCTCACCCAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">APEX1-g1-R  aaacCTGGGTGAGGTTTTCTGATCc</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">APEX1-g2-F  caccgGTAACGGGAATGCCGAAGCG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">APEX1-g2-R  aaacCGCTTCGGCATTCCCGTTACc</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3-g1.2-F  caccgAAACCAAGAGGATTTGCCAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3-g1.2-R  aaacCTGGCAAATCCTCTTGGTTTc</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3-g2.2-F  caccgAGACTTGGTGCTGGCGAAAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3-g2.2-R  aaacCTTTCGCCAGCACCAAGTCTc</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EcoR1_FOXC1  aaaGAATTCatgcaggcgcgctac</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EcoR1_GATA6  aaaGAATTCatggccttgactgacggc</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EcoR1_SP1  aaaGAATTCatggactacaaagaccatga</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EcoR1_YY1  aaaGAATTCatggcctcgggcgacaccct</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FOXC1_BamH1  aaaGGATCCaaacttgctacagtcgtaga</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FOXC1_g1_F  CACCTCCAGCGGGAGCAGCCCCCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FOXC1_g1_R  AAACAGGTCGCCCTCGTCGGGGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FOXC1_g2_F  CACCGCGCCGCCGGAGCAGGCCGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FOXC1_g2_R  AAACCGCGGCGGCCTCGTCCGGCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GATA6_BamH1  aaaGGATCCggccagggccagg</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HOXB6_Not1  aaaGCGGCCGCCTCGGCCTGTTTTTCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JUN_Not1  aaaGCGGCCGCAAATGTTTGCAACTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JUN_OX_F  gggttaattaaATGACTGCAAAGATGGAAAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JUN_OX_R  aaagcggccgcAAATGTTTGCAAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pac1_HOXB6  aaaTTAATTAAATGAGTTCCTATTTCGTGAAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pac1_JUN  aaaTTAATTAAATGACTGCAAAGATG</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pac1_POU3F3  aaaTTAATTAAATGGCCACGGCGGCTT</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pac1_SMARCE1  aaaTTAATTAAATGTCAAAAAGACCA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pac1_STAT1  aaaTTAATTAAATGTCAAAAAGACCA</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pCBX3_F  AATTAATTAAATGgaattcggaaaaaaacag</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pCBX3_R  AAGCGGCCGCttgagcttcatcttctggacaa</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3_Not1  aaaGCGGCCGCCTGAACGCTCGTCTGCAGCCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3_OX_F  aaattaattaaATGGCCACGGCGGCTTCTAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3_OX_R  aaagcggccgcCTGAACGCTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3-g1-F  caccgTGGAGGCGAGCTCGCCG</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3-g1-R  aaacCGGCGAGCTCGCCTCCAc</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3-g2.2-F  caccggcggcgggtgaggatgcgcg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3-g2.2-R  aaaccgcgcatcctcacccgccgcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SP1_BamH1  aaaGGATCCgaagccattgccactgatat</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1_Not1  aaaGCGGCCGCTACTGTGTTCATCATACTGTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1_OX_F  gggttaattaaATGTCTCAGTGGTACGAACT</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1_OX_R  aaagcggccgcTACTGTGTTCATCATA</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1-g1-F  caccgTCAGACAGTACCTGGCACAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1-g1-R  aaacCTGTGCCAGGTACTGTCTGAc</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1-g2.2-F  caccgTCCACGGAATGAGACCATCG</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1-g2.2-R  aaacCGATGGTCTCATTCCGTGGAc</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Xba1_GATA6  aaaTCTAGAatggccttgactgacggc</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Xba1_SP1  aaaTCTAGAatggactacaaagaccatga</t>
         </is>
       </c>
     </row>
@@ -7055,7 +6208,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW  ·  umut  ·  0/81 full + 23 without a slot</t>
+          <t xml:space="preserve">Unkown FOR NOW  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -7167,175 +6320,6 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In this box, no slot recorded (23)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">APEX1_Not1  aaaGCGGCCGCCAGTGCTAGGTATAGGGTGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">APEX1_qPCR_F  TTGTGCTCGGGTTAGGAGGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">APEX1_qPCR_R  CCAGCGAAGCCCCTCTTATG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3-g1-F  caccgTGTGGCTTGAGCTGTAGGCG</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3-g1-R  aaacCGCCTACAGCTCAAGCCACAc</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3-g2-F  caccgCGCGACCCGGAGCAGCTCGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBX3-g2-R  aaacCCGAGCTGCTCCGGGTCGCGc</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pac1_APEX1  aaaTTAATTAAATGCCGAAGCGTGGGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3-g2-F  caccgAACGCGGGAGAAACGGACCA</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POU3F3-g2-R  aaacTGGTCCGTTTCTCCCGCGTTc</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shYY1-1-F  CCGGAGAACTCACCTCCTGATTATTCTCGAGAATAATCAGGAGGTGAGTTCTTTTTTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shYY1-1-R  AATTCAAAAAAGAACTCACCTCCTGATTATTCTCGAGAATAATCAGGAGGTGAGTTCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shYY1-2-F  CCGGCTCCTGATTATTCAGAATATACTCGAGTATATTCTGAATAATCAGGAGTTTTTG</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shYY1-2-R  AATTCAAAAACTCCTGATTATTCAGAATATACTCGAGTATATTCTGAATAATCAGGAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1_Not1  aaaGCGGCCGCTTCTTTTTTCTCATCTTCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1_OX_F  gggttaattaaATGTCAAAAAGACCATCTTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1_OX_R  aaagcggccgcTTCTTTTTTCTCATC</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1-g1-F  caccgTTTTGGAATCGTGATACCAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1-g1-R  aaacCTGGTATCACGATTCCAAAAc</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1-g2-F  caccgGGATTGTATCCCACAAACCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SMARCE1-g2-R  aaacGGGTTTGTGGGATACAATCCc</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1-g2-F  caccgGTTAACCTAGACAGCTCTCG</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAT1-g2-R  aaacCGAGAGCTGTCTAGGTTAACc</t>
         </is>
       </c>
     </row>
@@ -7356,7 +6340,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No use  ·  umut  ·  0/81 full + 14 without a slot</t>
+          <t xml:space="preserve">No use  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -7468,112 +6452,6 @@
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">In this box, no slot recorded (14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_C3_1_F  caccgTGAGAGCTAAACCTACCAGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_C3_1_R  aaacCCTGGTAGGTTTAGCTCTCA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_C3_2_F  caccgAGCCCCCCCAAATCATTTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_C3_2_R  aaacCTAAATGATTTGGGGGGGCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_C3_3_F  caccgTTCCAACAGGTTCCCCACAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_C3_3_F  caccgGCAGGGCTAGAGAATGGGCC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_C3_3_R  aaacATGTGGGGAACCTGTTGGAA</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_C3_3_R  aaacGGCCCATTCTCTAGCCCTGCc</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC5_F  caccgAGCCCCCCCAAATCATTTAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_gC5_R  aaacCTAAATGATTTGGGGGGGCTc</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_P1_F  caccgaGCTTGCTGGGAGAGCGGGA</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_P1_R  aaacTCCCGCTCTCCCAGCAAGCt</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_P2_F  caccgACGGTCCGGAGCAAGCCCAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AR_P2_R  aaacCTGGGCTTGCTCCGGACCGT</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -791,13 +791,13 @@
         <v>9</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>81</v>
       </c>
       <c r="I18">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -5101,7 +5101,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Common Box #1  ·  umut  ·  5/81 full</t>
         </is>
       </c>
     </row>
@@ -5157,6 +5157,31 @@
       <c r="A5" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -751,13 +751,13 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H17">
         <v>81</v>
       </c>
       <c r="I17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4649,7 +4649,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  64/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  63/81 full</t>
         </is>
       </c>
     </row>
@@ -4866,11 +4866,6 @@
       <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7 p15</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 3xFLAG p19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -19,13 +19,14 @@
     <sheet name="DUZENLE" sheetId="15" r:id="rId15"/>
     <sheet name="ONGOING" sheetId="16" r:id="rId16"/>
     <sheet name="UMUT CELLS -4-" sheetId="17" r:id="rId17"/>
-    <sheet name="Common Box #1" sheetId="18" r:id="rId18"/>
-    <sheet name="ChIP Box" sheetId="19" r:id="rId19"/>
-    <sheet name="ChIP Box -2-" sheetId="20" r:id="rId20"/>
-    <sheet name="Umut -20 -2-" sheetId="21" r:id="rId21"/>
-    <sheet name="Umut -20 Box -1-" sheetId="22" r:id="rId22"/>
-    <sheet name="Unkown FOR NOW" sheetId="23" r:id="rId23"/>
-    <sheet name="No use" sheetId="24" r:id="rId24"/>
+    <sheet name="Umut Cell Box -5-" sheetId="18" r:id="rId18"/>
+    <sheet name="Common Box #1" sheetId="19" r:id="rId19"/>
+    <sheet name="ChIP Box" sheetId="20" r:id="rId20"/>
+    <sheet name="ChIP Box -2-" sheetId="21" r:id="rId21"/>
+    <sheet name="Umut -20 -2-" sheetId="22" r:id="rId22"/>
+    <sheet name="Umut -20 Box -1-" sheetId="23" r:id="rId23"/>
+    <sheet name="Unkown FOR NOW" sheetId="24" r:id="rId24"/>
+    <sheet name="No use" sheetId="25" r:id="rId25"/>
   </sheets>
 </workbook>
 </file>
@@ -771,12 +772,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">Umut Cell Box -5-</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -791,13 +792,13 @@
         <v>9</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="H18">
         <v>81</v>
       </c>
       <c r="I18">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -806,17 +807,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1 → Rack 1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -831,13 +832,13 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>81</v>
       </c>
       <c r="I19">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -856,7 +857,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -896,7 +897,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -936,7 +937,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -966,17 +967,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1 → Rack 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1016,7 +1017,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">No use</t>
+          <t xml:space="preserve">Unkown FOR NOW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1040,6 +1041,46 @@
         <v>81</v>
       </c>
       <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No use</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+      <c r="F25">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>81</v>
+      </c>
+      <c r="I25">
+        <v>81</v>
+      </c>
+      <c r="J25">
         <v>0</v>
       </c>
     </row>
@@ -5089,14 +5130,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1  ·  umut  ·  5/81 full</t>
+          <t xml:space="preserve">Umut Cell Box -5-  ·  umut  ·  73/81 full</t>
         </is>
       </c>
     </row>
@@ -5156,27 +5197,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">LNCX gNT p+27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">LNCX gP1 p+27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">LNCX gP2 p+27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">LNCX gP3 p+27</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">LNCX gP4 p+27</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC1 p+27</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC2 p+27</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC3 p+27</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gC4 p+27</t>
         </is>
       </c>
     </row>
@@ -5186,6 +5247,36 @@
           <t xml:space="preserve">B</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 24</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 18</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 18</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 18</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5193,6 +5284,41 @@
           <t xml:space="preserve">C</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 7</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 28</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 28</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 28</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 28</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 28</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 28</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5200,6 +5326,36 @@
           <t xml:space="preserve">D</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada +16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada +16</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada +16</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada +16</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada +16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada +16</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5207,6 +5363,51 @@
           <t xml:space="preserve">E</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 30</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5214,6 +5415,51 @@
           <t xml:space="preserve">F</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap Canada p+18</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5221,6 +5467,51 @@
           <t xml:space="preserve">G</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+19</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5228,11 +5519,101 @@
           <t xml:space="preserve">H</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX p+23</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR p13</t>
         </is>
       </c>
     </row>
@@ -5246,14 +5627,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1 → Rack 1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Common Box #1  ·  umut  ·  5/81 full</t>
         </is>
       </c>
     </row>
@@ -5309,6 +5690,31 @@
       <c r="A5" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
         </is>
       </c>
     </row>
@@ -5832,7 +6238,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">ChIP Box  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -5964,7 +6370,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">ChIP Box -2-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6502,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Umut -20 -2-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6221,14 +6627,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Umut -20 Box -1-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6360,6 +6766,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Unkown FOR NOW  ·  umut  ·  0/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t xml:space="preserve">No use  ·  umut  ·  0/81 full</t>
         </is>
       </c>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -752,13 +752,13 @@
         <v>9</v>
       </c>
       <c r="G17">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H17">
         <v>81</v>
       </c>
       <c r="I17">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -832,13 +832,13 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H19">
         <v>81</v>
       </c>
       <c r="I19">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -4690,7 +4690,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  63/81 full</t>
+          <t xml:space="preserve">UMUT CELLS -4-  ·  umut  ·  66/81 full</t>
         </is>
       </c>
     </row>
@@ -4783,6 +4783,11 @@
           <t xml:space="preserve">HEK 3xFLAG p21</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK pCDH-YY1 OX-2 31</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t xml:space="preserve">hek atf3 ox rep3 p28</t>
@@ -5065,6 +5070,16 @@
       <c r="G12" t="inlineStr">
         <is>
           <t xml:space="preserve">LUCX gC4 23</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gNT</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gNT</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5649,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1  ·  umut  ·  5/81 full</t>
+          <t xml:space="preserve">Common Box #1  ·  umut  ·  9/81 full</t>
         </is>
       </c>
     </row>
@@ -5722,6 +5737,26 @@
       <c r="A6" t="inlineStr">
         <is>
           <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP4</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP4</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gNT</t>
+          <t xml:space="preserve">LUCX gNT 26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gNT</t>
+          <t xml:space="preserve">LUCX gNT 26</t>
         </is>
       </c>
     </row>
@@ -5741,22 +5741,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LUCX gP2 26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LUCX gP2 26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP4</t>
+          <t xml:space="preserve">LUCX gP4 26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP4</t>
+          <t xml:space="preserve">LUCX gP4 26</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -27,6 +27,7 @@
     <sheet name="Umut -20 Box -1-" sheetId="23" r:id="rId23"/>
     <sheet name="Unkown FOR NOW" sheetId="24" r:id="rId24"/>
     <sheet name="No use" sheetId="25" r:id="rId25"/>
+    <sheet name="Big Plasmid Box" sheetId="26" r:id="rId26"/>
   </sheets>
 </workbook>
 </file>
@@ -1084,6 +1085,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Big Plasmid Box</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="E26">
+        <v>9</v>
+      </c>
+      <c r="F26">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>81</v>
+      </c>
+      <c r="I26">
+        <v>81</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -7052,6 +7093,138 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Big Plasmid Box  ·  umut  ·  0/81 full</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">F</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetData>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -20,14 +20,14 @@
     <sheet name="ONGOING" sheetId="16" r:id="rId16"/>
     <sheet name="UMUT CELLS -4-" sheetId="17" r:id="rId17"/>
     <sheet name="Umut Cell Box -5-" sheetId="18" r:id="rId18"/>
-    <sheet name="Common Box #1" sheetId="19" r:id="rId19"/>
-    <sheet name="ChIP Box" sheetId="20" r:id="rId20"/>
-    <sheet name="ChIP Box -2-" sheetId="21" r:id="rId21"/>
-    <sheet name="Umut -20 -2-" sheetId="22" r:id="rId22"/>
-    <sheet name="Umut -20 Box -1-" sheetId="23" r:id="rId23"/>
-    <sheet name="Unkown FOR NOW" sheetId="24" r:id="rId24"/>
-    <sheet name="No use" sheetId="25" r:id="rId25"/>
-    <sheet name="Big Plasmid Box" sheetId="26" r:id="rId26"/>
+    <sheet name="Big Plasmid Box" sheetId="19" r:id="rId19"/>
+    <sheet name="Common Box #1" sheetId="20" r:id="rId20"/>
+    <sheet name="ChIP Box" sheetId="21" r:id="rId21"/>
+    <sheet name="ChIP Box -2-" sheetId="22" r:id="rId22"/>
+    <sheet name="Umut -20 -2-" sheetId="23" r:id="rId23"/>
+    <sheet name="Umut -20 Box -1-" sheetId="24" r:id="rId24"/>
+    <sheet name="Unkown FOR NOW" sheetId="25" r:id="rId25"/>
+    <sheet name="No use" sheetId="26" r:id="rId26"/>
   </sheets>
 </workbook>
 </file>
@@ -813,12 +813,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1</t>
+          <t xml:space="preserve">Big Plasmid Box</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -833,13 +833,13 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H19">
         <v>81</v>
       </c>
       <c r="I19">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -848,17 +848,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1 → Rack 1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box</t>
+          <t xml:space="preserve">Common Box #1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -873,13 +873,13 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H20">
         <v>81</v>
       </c>
       <c r="I20">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-</t>
+          <t xml:space="preserve">ChIP Box</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-</t>
+          <t xml:space="preserve">ChIP Box -2-</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-</t>
+          <t xml:space="preserve">Umut -20 -2-</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1008,17 +1008,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1 → Rack 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW</t>
+          <t xml:space="preserve">Umut -20 Box -1-</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">No use</t>
+          <t xml:space="preserve">Unkown FOR NOW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Plasmid Box</t>
+          <t xml:space="preserve">No use</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5683,14 +5683,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Common Box #1  ·  umut  ·  9/81 full</t>
+          <t xml:space="preserve">Big Plasmid Box  ·  umut  ·  11/81 full</t>
         </is>
       </c>
     </row>
@@ -5750,27 +5750,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">HEK CuAdapt 0 60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">HEK CuAdapt CuCl2 100 60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">HEK CuAdapt CuCl2 100 60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">HEK CuAdapt CuSO4 100 60</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 p18</t>
+          <t xml:space="preserve">HEK CuAdapt CuSO4 200 60</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK CuAdapt CuSO4 400 60</t>
         </is>
       </c>
     </row>
@@ -5782,22 +5787,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2 26</t>
+          <t xml:space="preserve">HepG2 CuAdapt 0 28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2 26</t>
+          <t xml:space="preserve">HepG2 CuAdapt CuCl2 100 28</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP4 26</t>
+          <t xml:space="preserve">HepG2 CuAdapt CuCl2 200 28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP4 26</t>
+          <t xml:space="preserve">HepG2 CuAdapt CuSO4 100 28</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HepG2 CuAdapt CuSO4 200 28</t>
         </is>
       </c>
     </row>
@@ -6307,14 +6317,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridge 1 → Rack 1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Common Box #1  ·  umut  ·  9/81 full</t>
         </is>
       </c>
     </row>
@@ -6372,11 +6382,56 @@
           <t xml:space="preserve">A</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 p18</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP2 26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP2 26</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP4 26</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUCX gP4 26</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ChIP Box -2-  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">ChIP Box  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6633,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 -2-  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">ChIP Box -2-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6765,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut -20 Box -1-  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Umut -20 -2-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6835,14 +6890,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Fridge 1 → Rack 1</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unkown FOR NOW  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Umut -20 Box -1-  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -6974,7 +7029,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">No use  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">Unkown FOR NOW  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7161,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Plasmid Box  ·  umut  ·  0/81 full</t>
+          <t xml:space="preserve">No use  ·  umut  ·  0/81 full</t>
         </is>
       </c>
     </row>

--- a/cellstocks/exports/layout.xlsx
+++ b/cellstocks/exports/layout.xlsx
@@ -793,13 +793,13 @@
         <v>9</v>
       </c>
       <c r="G18">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H18">
         <v>81</v>
       </c>
       <c r="I18">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -833,13 +833,13 @@
         <v>9</v>
       </c>
       <c r="G19">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H19">
         <v>81</v>
       </c>
       <c r="I19">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -5193,7 +5193,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Umut Cell Box -5-  ·  umut  ·  73/81 full</t>
+          <t xml:space="preserve">Umut Cell Box -5-  ·  umut  ·  75/81 full</t>
         </is>
       </c>
     </row>
@@ -5410,6 +5410,16 @@
       <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">LnCap Canada +16</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNC478 #2 27</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNC478 #2 27</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5700,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Big Plasmid Box  ·  umut  ·  11/81 full</t>
+          <t xml:space="preserve">Big Plasmid Box  ·  umut  ·  13/81 full</t>
         </is>
       </c>
     </row>
@@ -5815,6 +5825,16 @@
       <c r="A7" t="inlineStr">
         <is>
           <t xml:space="preserve">C</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap ER +2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap ER +2</t>
         </is>
       </c>
     </row>
